--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,8 @@
           <t>2026-09-20 07:10:43</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -533,6 +531,292 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:46:03</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:46:03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:17:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana )</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:17:40</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella )</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:17:40</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,10 +652,8 @@
           <t>2026-09-20 08:17:40</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -710,10 +708,8 @@
           <t>2026-09-20 08:17:40</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B6" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -768,10 +764,8 @@
           <t>2026-09-20 08:17:40</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B7" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -817,6 +811,1244 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:36:57</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:36:57</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:36:57</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:36:57</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>22</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:36:57</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:36:57</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:36:57</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:28</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:28</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:28</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:28</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:28</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:28</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:29:10</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:29:10</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:29:10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>25</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:29:10</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:29:10</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>25</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:29:10</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>22</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:36:16</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:36:16</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:36:16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>21</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1884,10 +1884,8 @@
           <t>2026-09-20 11:36:16</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B27" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1942,10 +1940,8 @@
           <t>2026-09-20 11:36:16</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2000,10 +1996,8 @@
           <t>2026-09-20 11:36:16</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2049,6 +2043,176 @@
       <c r="L29" t="inlineStr">
         <is>
           <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:42:50</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:22:43</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>24</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:55:18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -1209,7 +1209,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:28</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1235,20 +1235,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.48</v>
+        <v>25</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1258,14 +1258,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:28</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1291,37 +1291,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.48</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:28</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1370,14 +1370,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:28</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1403,37 +1403,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.74</v>
+        <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:28</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1459,20 +1459,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:28</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1515,20 +1515,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1538,14 +1538,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-20 11:36:16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1571,16 +1571,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1589,19 +1589,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-20 11:36:16</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1627,16 +1627,16 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1645,19 +1645,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-20 11:36:16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1683,16 +1683,16 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1706,14 +1706,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-21 09:42:50</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1731,45 +1731,45 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-21 11:22:43</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,45 +1787,45 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-21 11:55:18</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1847,24 +1847,24 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>316.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1874,22 +1874,24 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:57</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1907,45 +1909,47 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>0.48</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:57</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1963,20 +1967,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>0.48</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1986,22 +1990,24 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:57</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2024,15 +2030,15 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>0.74</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2042,22 +2048,24 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21 09:42:50</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:57</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2067,11 +2075,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2080,40 +2088,42 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21 11:22:43</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:57</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2123,45 +2133,45 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>0.74</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21 11:55:18</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2171,7 +2181,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2185,24 +2195,24 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>316.8</v>
+        <v>0.74</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2212,7 +2222,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -1713,7 +1713,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21 09:42:50</t>
+          <t>2026-09-21 11:22:43</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1739,37 +1739,37 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21 11:22:43</t>
+          <t>2026-09-21 11:55:18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1795,37 +1795,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>316.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 11:55:18</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1856,15 +1856,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>316.8</v>
+        <v>0.48</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -1884,10 +1884,8 @@
           <t>2026-09-22 10:56:57</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B27" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1905,7 +1903,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1914,7 +1912,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1932,7 +1930,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -1942,10 +1940,8 @@
           <t>2026-09-22 10:56:57</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1963,20 +1959,20 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1990,7 +1986,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
@@ -2000,10 +1996,8 @@
           <t>2026-09-22 10:56:57</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2021,7 +2015,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2048,7 +2042,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
@@ -2058,10 +2052,8 @@
           <t>2026-09-22 10:56:57</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B30" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2079,7 +2071,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2088,7 +2080,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2106,7 +2098,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
@@ -2116,10 +2108,8 @@
           <t>2026-09-22 10:56:57</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B31" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2137,7 +2127,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2171,7 +2161,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
+          <t>2026-09-24 09:51:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2181,7 +2171,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2191,11 +2181,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2204,25 +2194,25 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -817,7 +817,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 09:36:57</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -843,37 +843,37 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 09:36:57</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -899,37 +899,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 09:36:57</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -955,20 +955,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -978,14 +978,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 09:36:57</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1011,37 +1011,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 09:36:57</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1067,20 +1067,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1090,14 +1090,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 09:36:57</t>
+          <t>2026-09-20 10:29:10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1123,20 +1123,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1146,14 +1146,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 09:36:57</t>
+          <t>2026-09-20 11:36:16</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1175,41 +1175,41 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>7</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PERSONEL ON CALL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Mechanic/ Electrician</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>23</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-20 11:36:16</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1231,20 +1231,20 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1258,14 +1258,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-20 11:36:16</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1287,20 +1287,20 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1309,19 +1309,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-21 11:22:43</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1339,45 +1339,45 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-21 11:55:18</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1399,41 +1399,41 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>316.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1455,24 +1455,24 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>0.48</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1511,24 +1511,24 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>0.48</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1538,14 +1538,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1576,32 +1576,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>0.74</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1632,15 +1632,15 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>0.74</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1650,14 +1650,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1688,15 +1688,15 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>0.74</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1706,14 +1706,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21 11:22:43</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1731,45 +1731,45 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>0.74</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21 11:55:18</t>
+          <t>2026-09-24 09:51:03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1795,45 +1795,47 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>316.8</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:02:48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1851,45 +1853,47 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.48</v>
+        <v>13</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:02:48</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1907,20 +1911,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.48</v>
+        <v>9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1930,22 +1934,24 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:02:48</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1963,20 +1969,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.74</v>
+        <v>17</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1986,22 +1992,24 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:02:48</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2019,20 +2027,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2042,22 +2050,24 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:02:48</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2075,20 +2085,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.74</v>
+        <v>21</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2098,22 +2108,24 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:02:48</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2131,20 +2143,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.74</v>
+        <v>23</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2154,14 +2166,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-24 09:51:03</t>
+          <t>2026-09-30 11:02:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2171,7 +2183,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2181,38 +2193,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -649,7 +649,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 08:17:40</t>
+          <t>2026-09-21 11:55:18</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -675,20 +675,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>316.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana )</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 08:17:40</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -727,24 +727,24 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>0.48</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -754,14 +754,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella )</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 08:17:40</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>24</v>
+        <v>0.48</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -810,14 +810,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -866,14 +866,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -895,41 +895,41 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>0.74</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -951,24 +951,24 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>0.74</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -978,14 +978,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-22 10:56:57</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1007,41 +1007,41 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>0.74</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-24 09:51:03</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1059,45 +1059,45 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 10:29:10</t>
+          <t>2026-09-30 11:48:28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1119,41 +1119,41 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
+          <t>2026-09-30 11:48:28</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1175,41 +1175,41 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
+          <t>2026-09-30 11:48:28</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1231,24 +1231,24 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1258,14 +1258,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 11:36:16</t>
+          <t>2026-09-30 11:48:28</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1287,24 +1287,24 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1314,14 +1314,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21 11:22:43</t>
+          <t>2026-09-30 11:48:28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1339,11 +1339,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1365,19 +1365,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:55:18</t>
+          <t>2026-09-30 11:48:28</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1399,24 +1399,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>316.8</v>
+        <v>23</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1426,14 +1426,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
+          <t>2026-09-30 11:48:28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1455,24 +1455,24 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.48</v>
+        <v>23</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
+          <t>2026-09-30 11:58:56</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1511,24 +1511,24 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.48</v>
+        <v>24</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1538,14 +1538,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana )</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
+          <t>2026-09-30 11:58:56</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1567,24 +1567,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.74</v>
+        <v>24</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella )</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
+          <t>2026-09-30 11:58:56</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1623,24 +1623,24 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.74</v>
+        <v>24</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1650,14 +1650,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
+          <t>2026-09-30 12:10:51</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1679,24 +1679,24 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1706,14 +1706,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:57</t>
+          <t>2026-09-30 12:10:51</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1735,41 +1735,41 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.74</v>
+        <v>15</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24 09:51:03</t>
+          <t>2026-09-30 12:10:51</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,55 +1787,53 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-30 11:02:48</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:10:51</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1849,51 +1847,49 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30 11:02:48</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:10:51</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1907,24 +1903,24 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1934,24 +1930,22 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-30 11:02:48</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:10:51</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1965,24 +1959,24 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1992,24 +1986,22 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30 11:02:48</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:17:19</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2023,51 +2015,49 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-30 11:02:48</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:17:19</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2081,24 +2071,24 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2108,24 +2098,22 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30 11:02:48</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:17:19</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2139,24 +2127,24 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2166,14 +2154,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-30 11:02:48</t>
+          <t>2026-09-30 12:25:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2183,7 +2171,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2193,11 +2181,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2206,11 +2194,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2219,12 +2207,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2164,10 +2164,8 @@
           <t>2026-09-30 12:25:23</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B32" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2213,6 +2211,64 @@
       <c r="L32" t="inlineStr">
         <is>
           <t>Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:47:10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2220,10 +2220,8 @@
           <t>2026-10-01 13:47:10</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B33" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2269,6 +2267,120 @@
       <c r="L33" t="inlineStr">
         <is>
           <t>Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:17:07</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:42:07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus  2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2332,10 +2332,8 @@
           <t>2026-10-02 09:42:07</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B35" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2381,6 +2379,576 @@
       <c r="L35" t="inlineStr">
         <is>
           <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus  2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:28</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>16</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:28</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:28</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:28</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:28</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:57</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:57</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:57</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:57</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>105</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:57</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2668,10 +2668,8 @@
           <t>2026-10-03 13:04:57</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B41" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2726,10 +2724,8 @@
           <t>2026-10-03 13:04:57</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B42" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2784,10 +2780,8 @@
           <t>2026-10-03 13:04:57</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B43" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2842,10 +2836,8 @@
           <t>2026-10-03 13:04:57</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B44" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2900,10 +2892,8 @@
           <t>2026-10-03 13:04:57</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B45" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2949,6 +2939,1024 @@
       <c r="L45" t="inlineStr">
         <is>
           <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:52:15</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3195</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:52:15</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1486.5</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:08:25</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>040/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:21:21</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>30</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas Nama Wanhar Renaldi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:21:21</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>30</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Malam atas Nama Ilsan Adjedar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:21:21</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>30</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:21:21</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>30</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:21:21</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>30</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:21:21</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>30</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:42:29</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>30</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:29:25</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>48</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:57:36</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>30</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:57:36</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>30</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28:02</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>30</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28:02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>30</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28:02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28:02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>4</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>30</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28:02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>30</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3676,10 +3676,8 @@
           <t>2026-10-06 13:28:02</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B59" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3734,10 +3732,8 @@
           <t>2026-10-06 13:28:02</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B60" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3792,10 +3788,8 @@
           <t>2026-10-06 13:28:02</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B61" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3850,10 +3844,8 @@
           <t>2026-10-06 13:28:02</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B62" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3908,10 +3900,8 @@
           <t>2026-10-06 13:28:02</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B63" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3957,6 +3947,456 @@
       <c r="L63" t="inlineStr">
         <is>
           <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:22:04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT, Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:22:04</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)  Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:22:04</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:22:04</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:22:04</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories, Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:22:04</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:55:36</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>048/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>458.4</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:06:08</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>050/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -3953,7 +3953,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-06 17:22:04</t>
+          <t>2026-10-06 17:55:36</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3984,15 +3984,15 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>458.4</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4002,14 +4002,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT, Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-06 17:22:04</t>
+          <t>2026-10-06 19:06:08</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4031,16 +4031,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4058,18 +4058,20 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)  Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-06 17:22:04</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:17:38</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -4087,16 +4089,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4114,18 +4116,20 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-06 17:22:04</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:17:38</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -4143,16 +4147,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4170,18 +4174,20 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Portac Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-06 17:22:04</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:17:38</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -4199,7 +4205,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4208,7 +4214,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4226,18 +4232,20 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories, Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-06 17:22:04</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:17:38</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -4255,7 +4263,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4264,7 +4272,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4282,22 +4290,24 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-06 17:55:36</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:17:38</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4311,24 +4321,24 @@
         </is>
       </c>
       <c r="F70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
         <v>1</v>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Laundry services</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>458.4</v>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4338,14 +4348,14 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-06 19:06:08</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4355,7 +4365,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4369,16 +4379,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4386,7 +4396,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4396,7 +4406,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,10 +4068,8 @@
           <t>2026-10-07 06:17:38</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B66" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -4126,10 +4124,8 @@
           <t>2026-10-07 06:17:38</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B67" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -4184,10 +4180,8 @@
           <t>2026-10-07 06:17:38</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B68" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -4242,10 +4236,8 @@
           <t>2026-10-07 06:17:38</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B69" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -4300,10 +4292,8 @@
           <t>2026-10-07 06:17:38</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B70" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -4358,10 +4348,8 @@
           <t>2026-10-07 06:17:38</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B71" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4407,6 +4395,800 @@
       <c r="L71" t="inlineStr">
         <is>
           <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:43:10</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:43:10</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:01:27</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:01:27</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:34</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:34</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:34</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:34</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>4</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:34</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:36:17</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:36:17</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:36:17</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:36:17</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:36:17</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -2945,7 +2945,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-06 09:52:15</t>
+          <t>2026-10-06 10:08:25</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2971,20 +2971,20 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2994,14 +2994,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-06 09:52:15</t>
+          <t>2026-10-06 11:21:21</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3023,24 +3023,24 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1486.5</v>
+        <v>30</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
+          <t>Operator Crane Shift Siang atas Nama Wanhar Renaldi</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-06 10:08:25</t>
+          <t>2026-10-06 11:21:21</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+          <t>Operator Crane Shift Malam atas Nama Ilsan Adjedar</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas Nama Wanhar Renaldi</t>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam atas Nama Ilsan Adjedar</t>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3330,14 +3330,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-06 11:21:21</t>
+          <t>2026-10-06 11:42:29</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3386,14 +3386,14 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-06 11:21:21</t>
+          <t>2026-10-06 12:29:25</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3424,32 +3424,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+          <t>PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-06 11:42:29</t>
+          <t>2026-10-06 12:57:36</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3498,14 +3498,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-06 12:29:25</t>
+          <t>2026-10-06 12:57:36</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3523,45 +3523,45 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-06 12:57:36</t>
+          <t>2026-10-06 13:28:02</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3610,14 +3610,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-06 12:57:36</t>
+          <t>2026-10-06 13:28:02</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3816,11 +3816,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3834,14 +3834,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-06 13:28:02</t>
+          <t>2026-10-06 17:55:36</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3863,24 +3863,24 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-06 13:28:02</t>
+          <t>2026-10-06 19:06:08</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3919,24 +3919,24 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3946,14 +3946,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-06 17:55:36</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3984,15 +3984,15 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>458.4</v>
+        <v>1</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4002,14 +4002,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-06 19:06:08</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4031,16 +4031,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t>Portac Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4087,16 +4087,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4143,16 +4143,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Portac Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4289,7 +4289,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:38</t>
+          <t>2026-10-07 08:43:10</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4307,11 +4307,11 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4328,24 +4328,24 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:38</t>
+          <t>2026-10-07 08:43:10</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4363,11 +4363,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4384,24 +4384,24 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-07 08:43:10</t>
+          <t>2026-10-07 09:01:27</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4450,14 +4450,14 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-07 08:43:10</t>
+          <t>2026-10-07 09:01:27</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:27</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -4539,12 +4539,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4557,19 +4557,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:27</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4811,11 +4811,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4837,19 +4837,19 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4867,11 +4867,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4908,10 +4908,8 @@
           <t>2026-10-07 10:36:17</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B81" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4929,7 +4927,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4938,7 +4936,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4956,7 +4954,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
@@ -4966,10 +4964,8 @@
           <t>2026-10-07 10:36:17</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B82" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4987,16 +4983,16 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5014,7 +5010,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
@@ -5024,10 +5020,8 @@
           <t>2026-10-07 10:36:17</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B83" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -5045,16 +5039,16 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5062,7 +5056,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5072,14 +5066,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
+          <t>2026-10-07 11:58:29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5089,7 +5083,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5099,11 +5093,11 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5112,32 +5106,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>3195</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
+          <t>2026-10-07 11:58:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5147,7 +5141,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5157,11 +5151,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5170,11 +5164,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1488</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5183,12 +5177,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -3561,7 +3561,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-06 13:28:02</t>
+          <t>2026-10-06 17:55:36</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3587,20 +3587,20 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3610,14 +3610,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-06 13:28:02</t>
+          <t>2026-10-06 19:06:08</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3639,24 +3639,24 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-06 13:28:02</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3695,24 +3695,24 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3722,14 +3722,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t xml:space="preserve"> Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-06 13:28:02</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3751,24 +3751,24 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Portac Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-06 13:28:02</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3807,24 +3807,24 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3834,14 +3834,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-06 17:55:36</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3863,24 +3863,24 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>458.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-06 19:06:08</t>
+          <t>2026-10-07 06:17:38</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3919,16 +3919,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve"> Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4002,14 +4002,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:38</t>
+          <t>2026-10-07 08:43:10</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4027,20 +4027,20 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4048,24 +4048,24 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Portac Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:38</t>
+          <t>2026-10-07 08:43:10</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4083,11 +4083,11 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4104,24 +4104,24 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:38</t>
+          <t>2026-10-07 09:01:27</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4139,20 +4139,20 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4160,24 +4160,24 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:38</t>
+          <t>2026-10-07 09:01:27</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4195,20 +4195,20 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4216,24 +4216,24 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-07 06:17:38</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4272,24 +4272,24 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-07 08:43:10</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4307,20 +4307,20 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4333,19 +4333,19 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07 08:43:10</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4363,20 +4363,20 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4389,19 +4389,19 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:27</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4419,20 +4419,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:27</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4475,20 +4475,20 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4496,24 +4496,24 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4557,19 +4557,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4669,19 +4669,19 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4725,19 +4725,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4781,19 +4781,19 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
+          <t>2026-10-07 11:58:29</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -4819,37 +4819,37 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3195</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
+          <t>2026-10-07 11:58:29</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -4875,45 +4875,47 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1488</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:59:06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4923,53 +4925,55 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:59:06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4979,53 +4983,55 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:59:06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5035,45 +5041,45 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:29</t>
+          <t>2026-10-10 08:59:06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5083,7 +5089,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5097,24 +5103,24 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5124,14 +5130,14 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:29</t>
+          <t>2026-10-10 08:59:06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5141,7 +5147,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5155,24 +5161,24 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5182,7 +5188,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4908,10 +4908,8 @@
           <t>2026-10-10 08:59:06</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B81" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4966,10 +4964,8 @@
           <t>2026-10-10 08:59:06</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B82" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -5024,10 +5020,8 @@
           <t>2026-10-10 08:59:06</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B83" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -5082,10 +5076,8 @@
           <t>2026-10-10 08:59:06</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B84" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -5140,10 +5132,8 @@
           <t>2026-10-10 08:59:06</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B85" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -5189,6 +5179,120 @@
       <c r="L85" t="inlineStr">
         <is>
           <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:27:41</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:36:09</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>052/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4793,7 +4793,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:29</t>
+          <t>2026-10-10 08:59:06</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4819,20 +4819,20 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:29</t>
+          <t>2026-10-10 08:59:06</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4875,20 +4875,20 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5048,11 +5048,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5066,14 +5066,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-10 08:59:06</t>
+          <t>2026-10-13 10:27:41</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5091,45 +5091,45 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-10 08:59:06</t>
+          <t>2026-10-13 10:36:09</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5147,45 +5147,45 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-13 10:27:41</t>
+          <t>2026-10-15 17:39:11</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -5211,16 +5211,16 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5229,70 +5229,184 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational Consumption</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-13 10:36:09</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
+          <t>2026-10-15 17:39:11</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Operational side consumption</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1157</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:45:19</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>PROVISIONAL SUM</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>At Cost + Fee 15%</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>operational consumption</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>3195</v>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:45:19</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Operational side consumption</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>1488</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_basp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_basp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4009,7 +4009,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-07 08:43:10</t>
+          <t>2026-10-07 09:01:27</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4058,14 +4058,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-07 08:43:10</t>
+          <t>2026-10-07 09:01:27</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4114,14 +4114,14 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:27</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:27</t>
+          <t>2026-10-07 09:33:34</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4394,14 +4394,14 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4419,11 +4419,11 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:34</t>
+          <t>2026-10-07 10:36:17</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
@@ -4591,16 +4591,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
@@ -4647,16 +4647,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4674,14 +4674,14 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
+          <t>2026-10-10 08:59:06</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4699,45 +4699,45 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-07 10:36:17</t>
+          <t>2026-10-10 08:59:06</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4755,38 +4755,38 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4936,11 +4936,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-10 08:59:06</t>
+          <t>2026-10-13 10:27:41</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4979,45 +4979,45 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-10 08:59:06</t>
+          <t>2026-10-13 10:36:09</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5035,45 +5035,45 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-13 10:27:41</t>
+          <t>2026-10-15 17:39:11</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -5099,16 +5099,16 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5117,19 +5117,19 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational Consumption</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-13 10:36:09</t>
+          <t>2026-10-15 17:39:11</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5147,24 +5147,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1157</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5173,19 +5173,19 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-15 17:39:11</t>
+          <t>2026-10-15 17:45:19</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2578</v>
+        <v>3195</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5229,19 +5229,19 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational Consumption</t>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-15 17:39:11</t>
+          <t>2026-10-15 17:45:19</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1157</v>
+        <v>1488</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5285,19 +5285,19 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-15 17:45:19</t>
+          <t>2026-10-16 11:52:28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -5325,16 +5325,16 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>operational consumption</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3195</v>
+        <v>4</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5343,70 +5343,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption Periode 01 sd 30 September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-10-15 17:45:19</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Operational side consumption</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>1488</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption Periode 01 sd 30 September 2026</t>
+          <t>Mobilisasi 2 Unit Lighting Tower dan 2 Unit Mesin Genset 80 KVA dari Luwuk ke Senoro Cluster B</t>
         </is>
       </c>
     </row>
